--- a/js/spells.xlsx
+++ b/js/spells.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="11171" windowHeight="4452"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,12 +29,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="100">
+  <si>
+    <t>name</t>
+  </si>
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
+    <t>selectable</t>
   </si>
   <si>
     <t>desc</t>
@@ -52,52 +55,283 @@
     <t>slots</t>
   </si>
   <si>
+    <t>slotDisplay</t>
+  </si>
+  <si>
+    <t>conditionId</t>
+  </si>
+  <si>
     <t>effectId</t>
   </si>
   <si>
-    <t>mix</t>
-  </si>
-  <si>
-    <t>混合</t>
-  </si>
-  <si>
-    <t>获得药水 X＋Y</t>
+    <t>passiveId</t>
+  </si>
+  <si>
+    <t>descFnId</t>
+  </si>
+  <si>
+    <t>基本反应: 研磨</t>
+  </si>
+  <si>
+    <t>grind</t>
+  </si>
+  <si>
+    <t>获得药水(X＋Y). &lt;span class='italic'&gt;无冷却.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>["X","Y"]</t>
+  </si>
+  <si>
+    <t>always</t>
+  </si>
+  <si>
+    <t>基本反应: 过滤</t>
   </si>
   <si>
     <t>filter</t>
   </si>
   <si>
-    <t>过滤</t>
-  </si>
-  <si>
-    <t>获得药水 X－Y</t>
+    <t>获得药水(X－Y). &lt;span class='italic'&gt;无冷却.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>基本反应: 灼烧</t>
   </si>
   <si>
     <t>burn</t>
   </si>
   <si>
-    <t>燃烧</t>
-  </si>
-  <si>
-    <t>获得药水 X×Y</t>
+    <t>获得药水(X×Y). &lt;span class='italic'&gt;无冷却.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>基本反应: 萃取</t>
   </si>
   <si>
     <t>extract</t>
   </si>
   <si>
-    <t>萃取</t>
-  </si>
-  <si>
-    <t>获得药水 X÷Y</t>
+    <t>获得药水(X÷Y). &lt;span class='italic'&gt;无冷却.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>y_not_zero</t>
+  </si>
+  <si>
+    <t>活化</t>
   </si>
   <si>
     <t>activate</t>
   </si>
   <si>
-    <t>活化</t>
-  </si>
-  <si>
-    <t>获得药水 X＋1</t>
+    <t>获得药水(X＋1).</t>
+  </si>
+  <si>
+    <t>["X"]</t>
+  </si>
+  <si>
+    <t>激化</t>
+  </si>
+  <si>
+    <t>intensify</t>
+  </si>
+  <si>
+    <t>获得药水(2X).</t>
+  </si>
+  <si>
+    <t>冷冻</t>
+  </si>
+  <si>
+    <t>freezing</t>
+  </si>
+  <si>
+    <t>获得一份原料[♦1].</t>
+  </si>
+  <si>
+    <t>[]</t>
+  </si>
+  <si>
+    <t>拟态复制</t>
+  </si>
+  <si>
+    <t>mimic_copy</t>
+  </si>
+  <si>
+    <t>获得填入手牌的两份复制.</t>
+  </si>
+  <si>
+    <t>规模扩张</t>
+  </si>
+  <si>
+    <t>scale_expand</t>
+  </si>
+  <si>
+    <t>随机获得一份原料.</t>
+  </si>
+  <si>
+    <t>丰饶大地</t>
+  </si>
+  <si>
+    <t>fertile_land</t>
+  </si>
+  <si>
+    <t>随机获得两份原料.</t>
+  </si>
+  <si>
+    <t>灰色交易</t>
+  </si>
+  <si>
+    <t>grey_trade</t>
+  </si>
+  <si>
+    <t>需求与协会订单相同. 随机获得三份原料.</t>
+  </si>
+  <si>
+    <t>association_match</t>
+  </si>
+  <si>
+    <t>计算误差</t>
+  </si>
+  <si>
+    <t>calculation_error</t>
+  </si>
+  <si>
+    <t>获得四份随机原料.</t>
+  </si>
+  <si>
+    <t>["(23)"]</t>
+  </si>
+  <si>
+    <t>value_23</t>
+  </si>
+  <si>
+    <t>会员注册</t>
+  </si>
+  <si>
+    <t>membership_register</t>
+  </si>
+  <si>
+    <t>向原料供应商注册终身会员!</t>
+  </si>
+  <si>
+    <t>["[♠X]","[♥X]","[♣X]","[♦X]"]</t>
+  </si>
+  <si>
+    <t>all_suits_ingredient_same_value</t>
+  </si>
+  <si>
+    <t>终身会员!</t>
+  </si>
+  <si>
+    <t>membership_lifetime</t>
+  </si>
+  <si>
+    <t>获得一份随机类型的原料[X].</t>
+  </si>
+  <si>
+    <t>异变</t>
+  </si>
+  <si>
+    <t>cyclic_mutate</t>
+  </si>
+  <si>
+    <t>获得原料[X+1].</t>
+  </si>
+  <si>
+    <t>["[X]"]</t>
+  </si>
+  <si>
+    <t>ingredient_only</t>
+  </si>
+  <si>
+    <t>快速降温</t>
+  </si>
+  <si>
+    <t>quick_cool</t>
+  </si>
+  <si>
+    <t>获得原料[X-1]. 完成订单后结束冷却.</t>
+  </si>
+  <si>
+    <t>quick_cool_passive</t>
+  </si>
+  <si>
+    <t>周期律</t>
+  </si>
+  <si>
+    <t>cycle_law</t>
+  </si>
+  <si>
+    <t>获得原料[X+1]. &lt;span class='italic'&gt;施放法术后切换至下一形态.&lt;/span&gt;</t>
+  </si>
+  <si>
+    <t>cycle_law_passive</t>
+  </si>
+  <si>
+    <t>cycle_law_desc</t>
+  </si>
+  <si>
+    <t>战术快递</t>
+  </si>
+  <si>
+    <t>tactical_delivery</t>
+  </si>
+  <si>
+    <t>开局: 获得两份原料.</t>
+  </si>
+  <si>
+    <t>tactical_delivery_passive</t>
+  </si>
+  <si>
+    <t>伪造的奖章</t>
+  </si>
+  <si>
+    <t>fake_medal</t>
+  </si>
+  <si>
+    <t>开局: 获得一个资质奖章.</t>
+  </si>
+  <si>
+    <t>fake_medal_passive</t>
+  </si>
+  <si>
+    <t>投影</t>
+  </si>
+  <si>
+    <t>projection</t>
+  </si>
+  <si>
+    <t>获得原料[X], X等于你的其余手牌数.</t>
+  </si>
+  <si>
+    <t>镜中取影</t>
+  </si>
+  <si>
+    <t>mirror_reflection</t>
+  </si>
+  <si>
+    <t>复制最左侧的手牌.</t>
+  </si>
+  <si>
+    <t>["11"]</t>
+  </si>
+  <si>
+    <t>value_11</t>
+  </si>
+  <si>
+    <t>国士无双</t>
+  </si>
+  <si>
+    <t>thirteen_orphans</t>
+  </si>
+  <si>
+    <t>获得十三个资质奖章.</t>
+  </si>
+  <si>
+    <t>["[1]", "[2]", "[3]", "[4]",
+    "[5]", "[6]", "[7]", "[8]",
+    "[9]", "[10]", "[11]", "[12]",
+    "[13]", "[X]"]</t>
+  </si>
+  <si>
+    <t>thirteen_orphans_condition</t>
   </si>
 </sst>
 </file>
@@ -713,9 +947,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1028,18 +1268,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:M23"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
-    <col min="3" max="3" width="14.1111111111111" customWidth="1"/>
-    <col min="4" max="4" width="19.7777777777778" customWidth="1"/>
-    <col min="6" max="6" width="14.1111111111111" customWidth="1"/>
-    <col min="7" max="7" width="6.66666666666667" customWidth="1"/>
-    <col min="8" max="8" width="9.66666666666667" customWidth="1"/>
+    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="11.8888888888889" customWidth="1"/>
+    <col min="4" max="4" width="70.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="19.7777777777778" customWidth="1"/>
+    <col min="7" max="7" width="14.1111111111111" customWidth="1"/>
+    <col min="8" max="8" width="6.66666666666667" customWidth="1"/>
+    <col min="9" max="9" width="34.7777777777778" customWidth="1"/>
+    <col min="10" max="10" width="34.4444444444444" customWidth="1"/>
+    <col min="11" max="11" width="19.7777777777778" customWidth="1"/>
+    <col min="12" max="12" width="28.7777777777778" customWidth="1"/>
+    <col min="13" max="13" width="22" customWidth="1"/>
+    <col min="14" max="14" width="10.7777777777778" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1064,135 +1311,803 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-      <c r="F2">
+        <v>14</v>
+      </c>
+      <c r="C2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2">
         <v>-1</v>
       </c>
-      <c r="G2">
+      <c r="H2">
         <v>2</v>
       </c>
-      <c r="H2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3">
-        <v>0</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-      <c r="F3">
+        <v>19</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>-1</v>
       </c>
-      <c r="G3">
+      <c r="H3">
         <v>2</v>
       </c>
-      <c r="H3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" t="s">
+        <v>16</v>
+      </c>
+      <c r="J3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>-1</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5" t="b">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
+      </c>
+      <c r="I5" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8" t="s">
+        <v>38</v>
+      </c>
+      <c r="J8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9" t="b">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+      <c r="F10" t="b">
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10" t="s">
+        <v>38</v>
+      </c>
+      <c r="J10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11">
+        <v>5</v>
+      </c>
+      <c r="F11" t="b">
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11" t="s">
+        <v>38</v>
+      </c>
+      <c r="J11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:13">
+      <c r="A12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
+      </c>
+      <c r="F12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" t="s">
+        <v>51</v>
+      </c>
+      <c r="K12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" t="s">
+        <v>53</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13">
+        <v>2</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>55</v>
+      </c>
+      <c r="J13" t="s">
+        <v>56</v>
+      </c>
+      <c r="K13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+      <c r="F14" t="b">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>4</v>
+      </c>
+      <c r="I14" t="s">
+        <v>60</v>
+      </c>
+      <c r="J14" t="s">
+        <v>61</v>
+      </c>
+      <c r="K14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" t="s">
+        <v>62</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+      <c r="F15" t="b">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>0</v>
+      </c>
+      <c r="I15" t="s">
+        <v>38</v>
+      </c>
+      <c r="J15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" spans="1:13">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" t="b">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>67</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>68</v>
+      </c>
+      <c r="J16" t="s">
+        <v>69</v>
+      </c>
+      <c r="K16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17">
+        <v>3</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>68</v>
+      </c>
+      <c r="J17" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" t="s">
+        <v>71</v>
+      </c>
+      <c r="L17" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" t="s">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>76</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>68</v>
+      </c>
+      <c r="J18" t="s">
+        <v>69</v>
+      </c>
+      <c r="K18" t="s">
+        <v>75</v>
+      </c>
+      <c r="L18" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+      <c r="B19" t="s">
+        <v>80</v>
+      </c>
+      <c r="C19" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19" t="s">
+        <v>38</v>
+      </c>
+      <c r="J19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19"/>
+      <c r="L19" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C20" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>85</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20" t="s">
+        <v>38</v>
+      </c>
+      <c r="J20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>68</v>
+      </c>
+      <c r="J21" t="s">
+        <v>69</v>
+      </c>
+      <c r="K21" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B22" t="s">
+        <v>91</v>
+      </c>
+      <c r="C22" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>93</v>
+      </c>
+      <c r="J22" t="s">
+        <v>94</v>
+      </c>
+      <c r="K22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" ht="57.6" spans="1:13">
+      <c r="A23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" t="b">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>97</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+      <c r="F23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>-1</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>-1</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="b">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>20</v>
+      <c r="I23" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J23" t="s">
+        <v>99</v>
+      </c>
+      <c r="K23" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
